--- a/data/kz/niches/niche_formats_DENTAL.xlsx
+++ b/data/kz/niches/niche_formats_DENTAL.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -590,12 +591,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -645,12 +646,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -700,12 +701,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -755,12 +756,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -835,6 +836,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -890,12 +892,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -928,12 +930,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -966,12 +968,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1004,12 +1006,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1042,12 +1044,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1112,6 +1114,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1162,12 +1165,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1199,12 +1202,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1236,12 +1239,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1273,12 +1276,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1345,6 +1348,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1444,6 +1448,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1758,6 +1763,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1902,6 +1908,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1982,12 +1989,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2041,12 +2048,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2100,12 +2107,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2159,12 +2166,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2264,6 +2271,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2384,12 +2392,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2459,12 +2467,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2534,12 +2542,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2609,12 +2617,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -2720,6 +2728,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2790,12 +2799,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2837,12 +2846,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2880,12 +2889,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2923,12 +2932,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3006,6 +3015,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3076,12 +3086,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3121,12 +3131,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3166,12 +3176,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3211,12 +3221,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3289,6 +3299,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3344,12 +3355,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3386,12 +3397,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3428,12 +3439,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3470,12 +3481,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3548,6 +3559,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3618,12 +3630,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3679,12 +3691,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3740,12 +3752,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3801,12 +3813,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CLINIC</t>
+          <t>DENTAL_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3893,6 +3905,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3938,12 +3951,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3972,12 +3985,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -4006,12 +4019,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -4040,12 +4053,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -4101,6 +4114,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4126,12 +4140,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4148,12 +4162,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -4170,12 +4184,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -4192,12 +4206,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>DENTAL_CABINET</t>
+          <t>DENTAL_SOLO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
